--- a/data/data kemiringan robot pitch double support dengan hip (invers).xlsx
+++ b/data/data kemiringan robot pitch double support dengan hip (invers).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-8.565</v>
+        <v>-11.118</v>
       </c>
       <c r="C2" t="n">
-        <v>-35.501</v>
+        <v>-35.695</v>
       </c>
       <c r="D2" t="n">
-        <v>195.639</v>
+        <v>195.593</v>
       </c>
       <c r="E2" t="n">
         <v>18.243</v>
@@ -485,13 +485,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>-7.625</v>
+        <v>-13.979</v>
       </c>
       <c r="C3" t="n">
-        <v>-35.491</v>
+        <v>-35.698</v>
       </c>
       <c r="D3" t="n">
-        <v>195.852</v>
+        <v>195.447</v>
       </c>
       <c r="E3" t="n">
         <v>18.243</v>
@@ -505,13 +505,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>-12.805</v>
+        <v>-15.909</v>
       </c>
       <c r="C4" t="n">
-        <v>-35.49</v>
+        <v>-35.624</v>
       </c>
       <c r="D4" t="n">
-        <v>195.935</v>
+        <v>195.501</v>
       </c>
       <c r="E4" t="n">
         <v>18.243</v>
@@ -525,13 +525,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>-12.087</v>
+        <v>-17.863</v>
       </c>
       <c r="C5" t="n">
-        <v>-35.479</v>
+        <v>-35.674</v>
       </c>
       <c r="D5" t="n">
-        <v>195.896</v>
+        <v>195.574</v>
       </c>
       <c r="E5" t="n">
         <v>18.243</v>
@@ -545,13 +545,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>-16.307</v>
+        <v>-23.167</v>
       </c>
       <c r="C6" t="n">
-        <v>-35.471</v>
+        <v>-35.673</v>
       </c>
       <c r="D6" t="n">
-        <v>195.999</v>
+        <v>194.898</v>
       </c>
       <c r="E6" t="n">
         <v>18.243</v>
@@ -565,13 +565,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>-21.051</v>
+        <v>-21.698</v>
       </c>
       <c r="C7" t="n">
-        <v>-35.472</v>
+        <v>-35.651</v>
       </c>
       <c r="D7" t="n">
-        <v>195.621</v>
+        <v>195.463</v>
       </c>
       <c r="E7" t="n">
         <v>18.243</v>
@@ -585,13 +585,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>-20.499</v>
+        <v>-26.127</v>
       </c>
       <c r="C8" t="n">
-        <v>-35.467</v>
+        <v>-35.636</v>
       </c>
       <c r="D8" t="n">
-        <v>195.9</v>
+        <v>195.032</v>
       </c>
       <c r="E8" t="n">
         <v>18.243</v>
@@ -605,13 +605,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>-25.29</v>
+        <v>-28.977</v>
       </c>
       <c r="C9" t="n">
-        <v>-35.469</v>
+        <v>-35.644</v>
       </c>
       <c r="D9" t="n">
-        <v>195.477</v>
+        <v>194.624</v>
       </c>
       <c r="E9" t="n">
         <v>18.243</v>
@@ -625,13 +625,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>-27.215</v>
+        <v>-30.9</v>
       </c>
       <c r="C10" t="n">
-        <v>-35.466</v>
+        <v>-35.608</v>
       </c>
       <c r="D10" t="n">
-        <v>195.33</v>
+        <v>194.449</v>
       </c>
       <c r="E10" t="n">
         <v>18.243</v>
@@ -645,13 +645,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>-29.136</v>
+        <v>-34.437</v>
       </c>
       <c r="C11" t="n">
-        <v>-35.464</v>
+        <v>-35.618</v>
       </c>
       <c r="D11" t="n">
-        <v>195.149</v>
+        <v>193.566</v>
       </c>
       <c r="E11" t="n">
         <v>18.243</v>
@@ -665,13 +665,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>-31.636</v>
+        <v>-35.77</v>
       </c>
       <c r="C12" t="n">
-        <v>-35.465</v>
+        <v>-35.947</v>
       </c>
       <c r="D12" t="n">
-        <v>194.719</v>
+        <v>193.561</v>
       </c>
       <c r="E12" t="n">
         <v>18.243</v>
@@ -685,13 +685,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>-32.969</v>
+        <v>-38.273</v>
       </c>
       <c r="C13" t="n">
-        <v>-35.46</v>
+        <v>-35.948</v>
       </c>
       <c r="D13" t="n">
-        <v>194.687</v>
+        <v>193.083</v>
       </c>
       <c r="E13" t="n">
         <v>18.243</v>
@@ -705,13 +705,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>-34.898</v>
+        <v>-40.145</v>
       </c>
       <c r="C14" t="n">
-        <v>-35.791</v>
+        <v>-35.948</v>
       </c>
       <c r="D14" t="n">
-        <v>194.466</v>
+        <v>192.711</v>
       </c>
       <c r="E14" t="n">
         <v>18.243</v>
@@ -725,13 +725,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>-37.363</v>
+        <v>-42.066</v>
       </c>
       <c r="C15" t="n">
-        <v>-35.794</v>
+        <v>-35.946</v>
       </c>
       <c r="D15" t="n">
-        <v>193.901</v>
+        <v>192.408</v>
       </c>
       <c r="E15" t="n">
         <v>18.243</v>
@@ -742,16 +742,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>-39.289</v>
+        <v>-11.331</v>
       </c>
       <c r="C16" t="n">
-        <v>-35.792</v>
+        <v>-35.627</v>
       </c>
       <c r="D16" t="n">
-        <v>193.61</v>
+        <v>195.308</v>
       </c>
       <c r="E16" t="n">
         <v>18.243</v>
@@ -762,16 +762,16 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>15</v>
+        <v>-1</v>
       </c>
       <c r="B17" t="n">
-        <v>-42.415</v>
+        <v>-9.430999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>-35.469</v>
+        <v>-35.635</v>
       </c>
       <c r="D17" t="n">
-        <v>192.53</v>
+        <v>195.225</v>
       </c>
       <c r="E17" t="n">
         <v>18.243</v>
@@ -782,16 +782,16 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16</v>
+        <v>-2</v>
       </c>
       <c r="B18" t="n">
-        <v>-43.995</v>
+        <v>-6.881</v>
       </c>
       <c r="C18" t="n">
-        <v>-35.572</v>
+        <v>-35.64</v>
       </c>
       <c r="D18" t="n">
-        <v>192.139</v>
+        <v>195.223</v>
       </c>
       <c r="E18" t="n">
         <v>18.243</v>
@@ -802,16 +802,16 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="B19" t="n">
-        <v>-12</v>
+        <v>-4.987</v>
       </c>
       <c r="C19" t="n">
-        <v>-35.447</v>
+        <v>-35.648</v>
       </c>
       <c r="D19" t="n">
-        <v>195.27</v>
+        <v>195.079</v>
       </c>
       <c r="E19" t="n">
         <v>18.243</v>
@@ -822,16 +822,16 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="B20" t="n">
-        <v>-10.073</v>
+        <v>-3.07</v>
       </c>
       <c r="C20" t="n">
-        <v>-35.449</v>
+        <v>-35.658</v>
       </c>
       <c r="D20" t="n">
-        <v>195.136</v>
+        <v>194.851</v>
       </c>
       <c r="E20" t="n">
         <v>18.243</v>
@@ -842,16 +842,16 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="B21" t="n">
-        <v>-7.551</v>
+        <v>1.688</v>
       </c>
       <c r="C21" t="n">
-        <v>-35.448</v>
+        <v>-35.669</v>
       </c>
       <c r="D21" t="n">
-        <v>195.197</v>
+        <v>194.511</v>
       </c>
       <c r="E21" t="n">
         <v>18.243</v>
@@ -862,16 +862,16 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="B22" t="n">
-        <v>-2.83</v>
+        <v>3.59</v>
       </c>
       <c r="C22" t="n">
-        <v>-35.45</v>
+        <v>-35.681</v>
       </c>
       <c r="D22" t="n">
-        <v>195.104</v>
+        <v>194.183</v>
       </c>
       <c r="E22" t="n">
         <v>18.243</v>
@@ -882,16 +882,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="B23" t="n">
-        <v>-3.378</v>
+        <v>5.647</v>
       </c>
       <c r="C23" t="n">
-        <v>-35.455</v>
+        <v>-35.692</v>
       </c>
       <c r="D23" t="n">
-        <v>194.779</v>
+        <v>193.728</v>
       </c>
       <c r="E23" t="n">
         <v>18.243</v>
@@ -902,16 +902,16 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="B24" t="n">
-        <v>1.018</v>
+        <v>7.899</v>
       </c>
       <c r="C24" t="n">
-        <v>-35.46</v>
+        <v>-35.7</v>
       </c>
       <c r="D24" t="n">
-        <v>194.496</v>
+        <v>193.26</v>
       </c>
       <c r="E24" t="n">
         <v>18.243</v>
@@ -922,16 +922,16 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="B25" t="n">
-        <v>2.92</v>
+        <v>9.391999999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>-35.466</v>
+        <v>-35.718</v>
       </c>
       <c r="D25" t="n">
-        <v>194.167</v>
+        <v>192.952</v>
       </c>
       <c r="E25" t="n">
         <v>18.243</v>
@@ -942,16 +942,16 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="B26" t="n">
-        <v>4.977</v>
+        <v>14.23</v>
       </c>
       <c r="C26" t="n">
-        <v>-35.474</v>
+        <v>-35.735</v>
       </c>
       <c r="D26" t="n">
-        <v>193.713</v>
+        <v>192.096</v>
       </c>
       <c r="E26" t="n">
         <v>18.243</v>
@@ -962,16 +962,16 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="B27" t="n">
-        <v>7.201</v>
+        <v>15.028</v>
       </c>
       <c r="C27" t="n">
-        <v>-35.481</v>
+        <v>-35.741</v>
       </c>
       <c r="D27" t="n">
-        <v>193.295</v>
+        <v>192.122</v>
       </c>
       <c r="E27" t="n">
         <v>18.243</v>
@@ -982,16 +982,16 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="B28" t="n">
-        <v>9.083</v>
+        <v>21.724</v>
       </c>
       <c r="C28" t="n">
-        <v>-35.489</v>
+        <v>-35.754</v>
       </c>
       <c r="D28" t="n">
-        <v>192.859</v>
+        <v>191.329</v>
       </c>
       <c r="E28" t="n">
         <v>18.243</v>
@@ -1002,16 +1002,16 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="B29" t="n">
-        <v>12.334</v>
+        <v>20.447</v>
       </c>
       <c r="C29" t="n">
-        <v>-35.491</v>
+        <v>-35.768</v>
       </c>
       <c r="D29" t="n">
-        <v>192.729</v>
+        <v>191.221</v>
       </c>
       <c r="E29" t="n">
         <v>18.243</v>
@@ -1022,16 +1022,16 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="B30" t="n">
-        <v>14.56</v>
+        <v>25.028</v>
       </c>
       <c r="C30" t="n">
-        <v>-35.502</v>
+        <v>-35.792</v>
       </c>
       <c r="D30" t="n">
-        <v>192.124</v>
+        <v>190.164</v>
       </c>
       <c r="E30" t="n">
         <v>18.243</v>
@@ -1042,16 +1042,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="B31" t="n">
-        <v>21.054</v>
+        <v>26.841</v>
       </c>
       <c r="C31" t="n">
-        <v>-35.515</v>
+        <v>-35.81</v>
       </c>
       <c r="D31" t="n">
-        <v>191.349</v>
+        <v>189.478</v>
       </c>
       <c r="E31" t="n">
         <v>18.243</v>
@@ -1062,101 +1062,21 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-13</v>
+        <v>-16</v>
       </c>
       <c r="B32" t="n">
-        <v>19.776</v>
+        <v>25.92</v>
       </c>
       <c r="C32" t="n">
-        <v>-35.517</v>
+        <v>-35.819</v>
       </c>
       <c r="D32" t="n">
-        <v>191.228</v>
+        <v>189.259</v>
       </c>
       <c r="E32" t="n">
         <v>18.243</v>
       </c>
       <c r="F32" t="n">
-        <v>4.642</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>-14</v>
-      </c>
-      <c r="B33" t="n">
-        <v>24.358</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-35.536</v>
-      </c>
-      <c r="D33" t="n">
-        <v>190.183</v>
-      </c>
-      <c r="E33" t="n">
-        <v>18.243</v>
-      </c>
-      <c r="F33" t="n">
-        <v>4.642</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>-15</v>
-      </c>
-      <c r="B34" t="n">
-        <v>23.437</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-35.54</v>
-      </c>
-      <c r="D34" t="n">
-        <v>189.952</v>
-      </c>
-      <c r="E34" t="n">
-        <v>18.243</v>
-      </c>
-      <c r="F34" t="n">
-        <v>4.642</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>-16</v>
-      </c>
-      <c r="B35" t="n">
-        <v>25.25</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-35.552</v>
-      </c>
-      <c r="D35" t="n">
-        <v>189.266</v>
-      </c>
-      <c r="E35" t="n">
-        <v>18.243</v>
-      </c>
-      <c r="F35" t="n">
-        <v>4.642</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>-17</v>
-      </c>
-      <c r="B36" t="n">
-        <v>29.786</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-35.574</v>
-      </c>
-      <c r="D36" t="n">
-        <v>187.979</v>
-      </c>
-      <c r="E36" t="n">
-        <v>18.243</v>
-      </c>
-      <c r="F36" t="n">
         <v>4.642</v>
       </c>
     </row>
